--- a/Sindhi Muslim/Result Sheet/Class 3 - Students Result Sheet.xlsx
+++ b/Sindhi Muslim/Result Sheet/Class 3 - Students Result Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Result Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3092B8-BF8A-4BFE-9404-1B28EB30C161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C365D06-B106-44AB-9083-95C161171696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A3810461-FCAA-4427-95C3-213E25AAD5DA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="126">
   <si>
     <t>GOVERNMENT HIGH SCHOOL SINDHI JAMAAT CO-OPERATIVE HOUSING SOCIETY</t>
   </si>
@@ -115,9 +115,6 @@
   </si>
   <si>
     <t>Drawing</t>
-  </si>
-  <si>
-    <t>Grade</t>
   </si>
   <si>
     <t>Fiza</t>
@@ -547,6 +544,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -556,13 +560,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -894,96 +891,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
     </row>
     <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="10" t="s">
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="36.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
       <c r="F4" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>8</v>
@@ -995,7 +992,7 @@
         <v>9</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>10</v>
@@ -1003,81 +1000,65 @@
       <c r="L4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="7">
-        <v>100</v>
-      </c>
-      <c r="G5" s="7">
-        <v>100</v>
-      </c>
-      <c r="H5" s="7">
-        <v>100</v>
-      </c>
-      <c r="I5" s="7">
-        <v>100</v>
-      </c>
-      <c r="J5" s="7">
-        <v>100</v>
-      </c>
-      <c r="K5" s="7">
-        <v>100</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="7">
-        <v>600</v>
-      </c>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
     </row>
     <row r="6" spans="1:17" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>1</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>39</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -1097,14 +1078,14 @@
         <v>2</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="C8" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1124,14 +1105,14 @@
         <v>3</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>42</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1151,14 +1132,14 @@
         <v>4</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>32</v>
+      <c r="C10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1178,14 +1159,14 @@
         <v>5</v>
       </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>44</v>
+      <c r="D11" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1205,14 +1186,14 @@
         <v>6</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>46</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1232,14 +1213,14 @@
         <v>7</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>48</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1259,14 +1240,14 @@
         <v>8</v>
       </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>49</v>
+      <c r="D14" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1286,14 +1267,14 @@
         <v>9</v>
       </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>50</v>
+      <c r="C15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1313,14 +1294,14 @@
         <v>10</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>52</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1340,14 +1321,14 @@
         <v>11</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>54</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -1367,14 +1348,14 @@
         <v>12</v>
       </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>56</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1394,14 +1375,14 @@
         <v>13</v>
       </c>
       <c r="B19" s="2"/>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>58</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1421,14 +1402,14 @@
         <v>14</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>60</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1448,14 +1429,14 @@
         <v>15</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>62</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1475,14 +1456,14 @@
         <v>16</v>
       </c>
       <c r="B22" s="2"/>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>64</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1502,14 +1483,14 @@
         <v>17</v>
       </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -1529,14 +1510,14 @@
         <v>18</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>28</v>
+      <c r="C24" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -1556,14 +1537,14 @@
         <v>19</v>
       </c>
       <c r="B25" s="2"/>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>69</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -1583,14 +1564,14 @@
         <v>20</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="12" t="s">
-        <v>71</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -1610,14 +1591,14 @@
         <v>21</v>
       </c>
       <c r="B27" s="2"/>
-      <c r="C27" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>33</v>
+      <c r="C27" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -1637,14 +1618,14 @@
         <v>22</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" s="12" t="s">
+      <c r="C28" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -1664,14 +1645,14 @@
         <v>23</v>
       </c>
       <c r="B29" s="2"/>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1691,14 +1672,14 @@
         <v>24</v>
       </c>
       <c r="B30" s="2"/>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>75</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1718,14 +1699,14 @@
         <v>25</v>
       </c>
       <c r="B31" s="2"/>
-      <c r="C31" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>35</v>
+      <c r="C31" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -1745,14 +1726,14 @@
         <v>26</v>
       </c>
       <c r="B32" s="2"/>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>78</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1772,14 +1753,14 @@
         <v>27</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D33" s="12" t="s">
-        <v>80</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -1799,14 +1780,14 @@
         <v>28</v>
       </c>
       <c r="B34" s="2"/>
-      <c r="C34" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="12" t="s">
+      <c r="C34" s="9" t="s">
         <v>80</v>
       </c>
+      <c r="D34" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="E34" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1826,14 +1807,14 @@
         <v>29</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>83</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -1849,39 +1830,39 @@
       <c r="Q35" s="1"/>
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="13"/>
-      <c r="Q36" s="13"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11"/>
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>30</v>
       </c>
       <c r="B37" s="2"/>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1901,14 +1882,14 @@
         <v>31</v>
       </c>
       <c r="B38" s="2"/>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="12" t="s">
-        <v>87</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -1928,14 +1909,14 @@
         <v>32</v>
       </c>
       <c r="B39" s="2"/>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="12" t="s">
-        <v>89</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -1955,14 +1936,14 @@
         <v>33</v>
       </c>
       <c r="B40" s="2"/>
-      <c r="C40" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>90</v>
+      <c r="C40" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -1982,14 +1963,14 @@
         <v>34</v>
       </c>
       <c r="B41" s="2"/>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="12" t="s">
-        <v>92</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2009,14 +1990,14 @@
         <v>35</v>
       </c>
       <c r="B42" s="2"/>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>94</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -2036,14 +2017,14 @@
         <v>36</v>
       </c>
       <c r="B43" s="2"/>
-      <c r="C43" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" s="12" t="s">
+      <c r="C43" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -2063,14 +2044,14 @@
         <v>37</v>
       </c>
       <c r="B44" s="2"/>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="12" t="s">
-        <v>97</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2090,14 +2071,14 @@
         <v>38</v>
       </c>
       <c r="B45" s="2"/>
-      <c r="C45" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>31</v>
+      <c r="C45" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2117,14 +2098,14 @@
         <v>39</v>
       </c>
       <c r="B46" s="2"/>
-      <c r="C46" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>98</v>
+      <c r="C46" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>97</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2144,14 +2125,14 @@
         <v>40</v>
       </c>
       <c r="B47" s="2"/>
-      <c r="C47" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>30</v>
+      <c r="C47" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -2171,14 +2152,14 @@
         <v>41</v>
       </c>
       <c r="B48" s="2"/>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D48" s="12" t="s">
-        <v>101</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2198,14 +2179,14 @@
         <v>42</v>
       </c>
       <c r="B49" s="8"/>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D49" s="12" t="s">
-        <v>103</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2225,14 +2206,14 @@
         <v>43</v>
       </c>
       <c r="B50" s="2"/>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -2252,14 +2233,14 @@
         <v>44</v>
       </c>
       <c r="B51" s="2"/>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D51" s="12" t="s">
-        <v>107</v>
-      </c>
       <c r="E51" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -2279,14 +2260,14 @@
         <v>45</v>
       </c>
       <c r="B52" s="2"/>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D52" s="12" t="s">
-        <v>109</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -2306,14 +2287,14 @@
         <v>46</v>
       </c>
       <c r="B53" s="2"/>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D53" s="12" t="s">
-        <v>111</v>
-      </c>
       <c r="E53" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -2333,14 +2314,14 @@
         <v>47</v>
       </c>
       <c r="B54" s="2"/>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D54" s="12" t="s">
-        <v>113</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -2360,14 +2341,14 @@
         <v>48</v>
       </c>
       <c r="B55" s="2"/>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="12" t="s">
-        <v>115</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2387,14 +2368,14 @@
         <v>49</v>
       </c>
       <c r="B56" s="2"/>
-      <c r="C56" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56" s="12" t="s">
+      <c r="C56" s="9" t="s">
         <v>115</v>
       </c>
+      <c r="D56" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="E56" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -2414,14 +2395,14 @@
         <v>50</v>
       </c>
       <c r="B57" s="2"/>
-      <c r="C57" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>64</v>
+      <c r="C57" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -2441,14 +2422,14 @@
         <v>51</v>
       </c>
       <c r="B58" s="2"/>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D58" s="12" t="s">
-        <v>119</v>
-      </c>
       <c r="E58" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -2468,14 +2449,14 @@
         <v>52</v>
       </c>
       <c r="B59" s="2"/>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D59" s="12" t="s">
-        <v>121</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -2491,58 +2472,58 @@
       <c r="Q59" s="1"/>
     </row>
     <row r="60" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="14">
+      <c r="A60" s="10">
         <v>53</v>
       </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="12" t="s">
+      <c r="B60" s="10"/>
+      <c r="C60" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D60" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="E60" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="10"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="10"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
+    </row>
+    <row r="61" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="10">
+        <v>54</v>
+      </c>
+      <c r="B61" s="10"/>
+      <c r="C61" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="14"/>
-      <c r="P60" s="14"/>
-      <c r="Q60" s="14"/>
-    </row>
-    <row r="61" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="14">
-        <v>54</v>
-      </c>
-      <c r="B61" s="14"/>
-      <c r="C61" s="12" t="s">
+      <c r="D61" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D61" s="12" t="s">
-        <v>125</v>
-      </c>
       <c r="E61" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="14"/>
-      <c r="O61" s="14"/>
-      <c r="P61" s="14"/>
-      <c r="Q61" s="14"/>
+        <v>125</v>
+      </c>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="15">
